--- a/artfynd/A 31122-2025 artfynd.xlsx
+++ b/artfynd/A 31122-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>88574912</v>
+        <v>88575251</v>
       </c>
       <c r="B12" t="n">
-        <v>89392</v>
+        <v>95511</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1815,25 +1815,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>221944</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lopplummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Huperzia selago</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Bernh. ex Schrank &amp; Mart.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1843,10 +1843,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>488507.950752767</v>
+        <v>488565.8362613903</v>
       </c>
       <c r="R12" t="n">
-        <v>7003827.796634332</v>
+        <v>7003946.879178762</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>88575099</v>
+        <v>88574912</v>
       </c>
       <c r="B13" t="n">
-        <v>95519</v>
+        <v>89392</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,25 +1927,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>488496.1447293738</v>
+        <v>488507.950752767</v>
       </c>
       <c r="R13" t="n">
-        <v>7003816.090335243</v>
+        <v>7003827.796634332</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2027,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>88574908</v>
+        <v>88575099</v>
       </c>
       <c r="B14" t="n">
-        <v>89356</v>
+        <v>95519</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2043,21 +2043,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>488483.8491420805</v>
+        <v>488496.1447293738</v>
       </c>
       <c r="R14" t="n">
-        <v>7003793.993005539</v>
+        <v>7003816.090335243</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2139,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>88575385</v>
+        <v>88574908</v>
       </c>
       <c r="B15" t="n">
-        <v>89410</v>
+        <v>89356</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2151,25 +2151,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>488503.073161342</v>
+        <v>488483.8491420805</v>
       </c>
       <c r="R15" t="n">
-        <v>7003855.828903234</v>
+        <v>7003793.993005539</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2248,6 +2248,118 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>88575385</v>
+      </c>
+      <c r="B16" t="n">
+        <v>89410</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Svartstugubodarna, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>488503.073161342</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7003855.828903234</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Brunflo</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-10-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Albin Enetjärn</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
